--- a/evaluation_forms/045_public_speaking_observation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/045_public_speaking_observation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>general_impact_of_the_speaker</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>General Impression of the Speaker</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>communication_skills</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Communication Skills</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>body_language</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Body Language</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vocal_variance</t>
+          <t>speaker_speaking_speed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>vocal_variance</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Speaking Speed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -617,10 +633,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Nonverbal Cues</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>vocal_vocalizations</t>
+          <t>vocalizations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>vocal_vocalizations</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Vocalizations</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vocal_tone</t>
+          <t>speaker_tone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>vocal_tone</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Vocal Tone</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>vocal_volume</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>vocal_volume</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eye_contact</t>
+          <t>speaker_eye_contact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>eye_contact</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Eye Contact</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>body_language</t>
+          <t>speaker_confidence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>body_language</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>overall_impression</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Overall Impression</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>body_language</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>body_language</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>overall_impression</t>
+          <t>speaker_sitting_on_hands</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>overall_impression</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Sitting on hands</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>speaker_crossing_arms</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>additional_comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Crossing arms</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
+          <t>speaker_tapping_foot</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Tapping foot</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
+          <t>speaker_fidgeting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Fidgeting</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
+          <t>speaker_playing_with_hair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Playing with hair</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,15 +979,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
+          <t>speaker_biting_nails</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Biting nails</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -934,131 +1006,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
+          <t>speaker_rubbing_hands</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Rubbing hands</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>nonverbal_cues</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1075,12 +1036,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1069,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'fidgeting',_'zh':_'fidgeting'}}</t>
+          <t>fidgeting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Fidgeting', 'zh': 'Fidgeting'}}</t>
+          <t>Fidgeting</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1086,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'eye_contact',_'zh':_''}}</t>
+          <t>eye_contact</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Eye contact', 'zh': ''}}</t>
+          <t>Eye contact</t>
         </is>
       </c>
     </row>
@@ -1142,573 +1103,624 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'crossing_arms',_'zh':_''}}</t>
+          <t>crossing_arms</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Crossing arms', 'zh': ''}}</t>
+          <t>Crossing arms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vocal_vocalizations_choices</t>
+          <t>nonverbal_cues_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'stammering',_'zh':_''}}</t>
+          <t>playing_with_hands</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Stammering', 'zh': ''}}</t>
+          <t>Playing with hands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vocal_vocalizations_choices</t>
+          <t>nonverbal_cues_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'using_filler_words',_'zh':_''}}</t>
+          <t>biting_nails</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Using filler words', 'zh': ''}}</t>
+          <t>Biting nails</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vocal_vocalizations_choices</t>
+          <t>vocalizations_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'using_filler_phrases',_'zh':_''}}</t>
+          <t>stammering</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Using filler phrases', 'zh': ''}}</t>
+          <t>Stammering</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vocal_tone_choices</t>
+          <t>vocalizations_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'too_fast',_'zh':_''}}</t>
+          <t>using_filler_words</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Too fast', 'zh': ''}}</t>
+          <t>Using filler words</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vocal_tone_choices</t>
+          <t>vocalizations_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'too_slow',_'zh':_''}}</t>
+          <t>using_filler_phrases</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Too slow', 'zh': ''}}</t>
+          <t>Using filler phrases</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vocal_tone_choices</t>
+          <t>speaker_tone_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'too_loud',_'zh':_''}}</t>
+          <t>too_fast</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Too loud', 'zh': ''}}</t>
+          <t>Too fast</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vocal_tone_choices</t>
+          <t>speaker_tone_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'too_soft',_'zh':_''}}</t>
+          <t>too_slow</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Too soft', 'zh': ''}}</t>
+          <t>Too slow</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vocal_volume_choices</t>
+          <t>speaker_tone_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'too_loud',_'zh':_''}}</t>
+          <t>too_loud</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Too loud', 'zh': ''}}</t>
+          <t>Too loud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vocal_volume_choices</t>
+          <t>speaker_tone_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'too_soft',_'zh':_''}}</t>
+          <t>too_soft</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Too soft', 'zh': ''}}</t>
+          <t>Too soft</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>vocal_volume_choices</t>
+          <t>volume_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'just_right',_'zh':_''}}</t>
+          <t>too_loud</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Just right', 'zh': ''}}</t>
+          <t>Too loud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>eye_contact_choices</t>
+          <t>volume_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'no_eye_contact',_'zh':_''}}</t>
+          <t>too_soft</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'No eye contact', 'zh': ''}}</t>
+          <t>Too soft</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>eye_contact_choices</t>
+          <t>volume_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'minimal_eye_contact',_'zh':_''}}</t>
+          <t>just_right</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Minimal eye contact', 'zh': ''}}</t>
+          <t>Just right</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>eye_contact_choices</t>
+          <t>speaker_eye_contact_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'frequent_eye_contact',_'zh':_''}}</t>
+          <t>no_eye_contact</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Frequent eye contact', 'zh': ''}}</t>
+          <t>No eye contact</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_eye_contact_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'fidgeting',_'zh':_''}}</t>
+          <t>minimal_eye_contact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Fidgeting', 'zh': ''}}</t>
+          <t>Minimal eye contact</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_eye_contact_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'tapping_foot',_'zh':_''}}</t>
+          <t>frequent_eye_contact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Tapping foot', 'zh': ''}}</t>
+          <t>Frequent eye contact</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_sitting_on_hands_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'crossing_arms',_'zh':_''}}</t>
+          <t>no_sitting_on_hands</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Crossing arms', 'zh': ''}}</t>
+          <t>No sitting on hands</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_sitting_on_hands_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'tapping_pen',_'zh':_''}}</t>
+          <t>minimal_sitting_on_hands</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Tapping pen', 'zh': ''}}</t>
+          <t>Minimal sitting on hands</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_sitting_on_hands_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'playing_with_hair',_'zh':_''}}</t>
+          <t>frequent_sitting_on_hands</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Playing with hair', 'zh': ''}}</t>
+          <t>Frequent sitting on hands</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_crossing_arms_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'biting_nails',_'zh':_''}}</t>
+          <t>no_crossing_arms</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Biting nails', 'zh': ''}}</t>
+          <t>No crossing arms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_crossing_arms_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'sitting_on_hands',_'zh':_''}}</t>
+          <t>minimal_crossing_arms</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Sitting on hands', 'zh': ''}}</t>
+          <t>Minimal crossing arms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_crossing_arms_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'fidgeting',_'zh':_''}}</t>
+          <t>frequent_crossing_arms</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Fidgeting', 'zh': ''}}</t>
+          <t>Frequent crossing arms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_tapping_foot_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'playing_with_hands',_'zh':_''}}</t>
+          <t>no_tapping_foot</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Playing with hands', 'zh': ''}}</t>
+          <t>No tapping foot</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_tapping_foot_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'looking_down',_'zh':_''}}</t>
+          <t>minimal_tapping_foot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Looking down', 'zh': ''}}</t>
+          <t>Minimal tapping foot</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_tapping_foot_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'fidgeting',_'zh':_''}}</t>
+          <t>frequent_tapping_foot</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Fidgeting', 'zh': ''}}</t>
+          <t>Frequent tapping foot</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_fidgeting_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'rubbing_hands',_'zh':_''}}</t>
+          <t>no_fidgeting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Rubbing hands', 'zh': ''}}</t>
+          <t>No fidgeting</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_fidgeting_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'biting_nails',_'zh':_''}}</t>
+          <t>minimal_fidgeting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Biting nails', 'zh': ''}}</t>
+          <t>Minimal fidgeting</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_fidgeting_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'playing_with_hair',_'zh':_''}}</t>
+          <t>frequent_fidgeting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Playing with hair', 'zh': ''}}</t>
+          <t>Frequent fidgeting</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_playing_with_hair_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'fidgeting',_'zh':_''}}</t>
+          <t>no_playing_with_hair</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Fidgeting', 'zh': ''}}</t>
+          <t>No playing with hair</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_playing_with_hair_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'fidgeting',_'zh':_''}}</t>
+          <t>minimal_playing_with_hair</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Fidgeting', 'zh': ''}}</t>
+          <t>Minimal playing with hair</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_playing_with_hair_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'playing_with_hands',_'zh':_''}}</t>
+          <t>frequent_playing_with_hair</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Playing with hands', 'zh': ''}}</t>
+          <t>Frequent playing with hair</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_biting_nails_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'biting_nails',_'zh':_''}}</t>
+          <t>no_biting_nails</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Biting nails', 'zh': ''}}</t>
+          <t>No biting nails</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_biting_nails_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'rubbing_face',_'zh':_''}}</t>
+          <t>minimal_biting_nails</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Rubbing face', 'zh': ''}}</t>
+          <t>Minimal biting nails</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nonverbal_cues_choices</t>
+          <t>speaker_biting_nails_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'text':_{'en':_'rubbing_hands',_'zh':_''}}</t>
+          <t>frequent_biting_nails</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'text': {'en': 'Rubbing hands', 'zh': ''}}</t>
+          <t>Frequent biting nails</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>speaker_rubbing_hands_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>no_rubbing_hands</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>No rubbing hands</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>speaker_rubbing_hands_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>minimal_rubbing_hands</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Minimal rubbing hands</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>speaker_rubbing_hands_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>frequent_rubbing_hands</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Frequent rubbing hands</t>
         </is>
       </c>
     </row>
